--- a/output/pdf_financials_xlsx/NAR.xlsx
+++ b/output/pdf_financials_xlsx/NAR.xlsx
@@ -5921,25 +5921,25 @@
         <v>0</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.010988</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-0.014438</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.014213</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.014888</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.015113</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-0.049188</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="L91" s="3" t="n">
         <v>0</v>
@@ -5973,52 +5973,52 @@
         <v>0.450459</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.607963</v>
+        <v>0.674643</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.702933</v>
+        <v>0.736389</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.9127459999999999</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.938235</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.334073</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.985473</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.141778</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.143846</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.256791</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.972654</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.300452</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.343896</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.452097</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.798269</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.281911</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>6.46562</v>
       </c>
     </row>
     <row r="93">
@@ -10110,7 +10110,11 @@
           <t>Share-based payment reserve (Note 15)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -12218,7 +12222,11 @@
           <t>Share-based payment reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -12719,7 +12727,11 @@
           <t>Share-based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -12818,7 +12830,11 @@
           <t>Investment revaluation reserve (Note 4)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -13386,7 +13402,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -13479,7 +13499,11 @@
           <t>Investment revaluation reserve</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -14255,7 +14279,11 @@
           <t>Share-based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -14554,7 +14582,11 @@
           <t>Share-based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -14649,7 +14681,11 @@
           <t>Investment revaluation reserve</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NAR.xlsx
+++ b/output/pdf_financials_xlsx/NAR.xlsx
@@ -1029,19 +1029,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.008569999999999999</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00681</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001234</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000401</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1983,19 +1983,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.572888</v>
+        <v>-3.581458</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-2.902607</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.912325</v>
+        <v>-2.919135</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.083787</v>
+        <v>-2.085021</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.10605</v>
+        <v>0.105649</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.573703</v>
@@ -2099,19 +2099,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.572888</v>
+        <v>-3.581458</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-2.902607</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.911646</v>
+        <v>-2.918456</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.083192</v>
+        <v>-2.084426</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.106348</v>
+        <v>0.105947</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.572847</v>
@@ -2406,46 +2406,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.200486</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.126124</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.67196</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.047318</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.893755</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>9.396969</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.10292</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.50764</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.368124</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.7749509999999999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.509085</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.57955</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.091927</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.032414</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.271513</v>
@@ -2522,46 +2522,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.200486</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.126124</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.67196</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0045</v>
+        <v>0.051818</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.00105</v>
+        <v>2.894805</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.001275</v>
+        <v>9.398244</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.0005999999999999999</v>
+        <v>2.10352</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.000375</v>
+        <v>2.508015</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.127145</v>
+        <v>0.495269</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.119</v>
+        <v>0.8939510000000001</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1275</v>
+        <v>0.636585</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.07191699999999999</v>
+        <v>0.651467</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.0275</v>
+        <v>1.119427</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.01</v>
+        <v>1.042414</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.274429</v>
@@ -3218,46 +3218,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.245762</v>
+        <v>0.045276</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.151138</v>
+        <v>0.025014</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.704227</v>
+        <v>0.032267</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.047318</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.893755</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>9.413905</v>
+        <v>0.016936</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.167626</v>
+        <v>0.064706</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.523059</v>
+        <v>0.015419</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.430563</v>
+        <v>0.062439</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.790224</v>
+        <v>0.015273</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.516642</v>
+        <v>0.007557</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.612941</v>
+        <v>0.033391</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.121807</v>
+        <v>0.02988</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.049015</v>
+        <v>0.016601</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.005552</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
@@ -35468,7 +35468,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -37682,7 +37682,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E301" s="5" t="n">

--- a/output/pdf_financials_xlsx/NAR.xlsx
+++ b/output/pdf_financials_xlsx/NAR.xlsx
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.476876</v>
+        <v>-0.476876</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0.72218</v>
@@ -4425,52 +4425,52 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.062765</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.03124</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0325</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.274</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.288119</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.356727</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.1728</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.1884</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.1721</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.1917</v>
       </c>
     </row>
     <row r="68">
@@ -7070,40 +7070,40 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.094861</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009705</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015494</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014256</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.022599</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002087</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004191</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005167</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.017765</v>
       </c>
     </row>
     <row r="112">
@@ -7311,19 +7311,19 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.050786</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.119768</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.070581</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.135384</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
@@ -8442,40 +8442,40 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.094861</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009705</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015494</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014256</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.022599</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002087</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004191</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005167</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.017765</v>
       </c>
     </row>
     <row r="135">
@@ -8502,13 +8502,13 @@
         <v>-0.107178</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.768733</v>
+        <v>-0.863594</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.980621</v>
+        <v>-0.990326</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.852187</v>
+        <v>-0.867681</v>
       </c>
       <c r="J135" s="1" t="inlineStr">
         <is>
@@ -8516,28 +8516,28 @@
         </is>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.722682</v>
+        <v>-0.736938</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.616425</v>
+        <v>-0.639024</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-0.678275</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-0.503791</v>
+        <v>-0.505878</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-0.655668</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-0.548449</v>
+        <v>-0.55264</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-0.883306</v>
+        <v>-0.888473</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-0.96617</v>
+        <v>-0.983935</v>
       </c>
     </row>
   </sheetData>
@@ -18052,7 +18052,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -18218,7 +18222,11 @@
           <t>Proceeds from a private placement</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -21140,7 +21148,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -25189,7 +25201,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E172" s="5" t="n">
         <v>-0.476876</v>
       </c>
@@ -37981,7 +37997,11 @@
           <t>Future income tax recovery (Note 7)</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -39284,7 +39304,11 @@
           <t>Future income tax recovery (Note 8)</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E317" s="5" t="n">
         <v>0.476876</v>
       </c>
